--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73088</v>
+        <v>16.85009</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49743</v>
+        <v>16.52458</v>
       </c>
       <c r="E2" t="n">
-        <v>17.13456</v>
+        <v>16.72038</v>
       </c>
       <c r="F2" t="n">
-        <v>43.01734</v>
+        <v>42.20023</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05024</v>
+        <v>0.05102</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79778</v>
+        <v>1.81163</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.14932</v>
+        <v>17.1313</v>
       </c>
       <c r="D3" t="n">
-        <v>16.64002</v>
+        <v>16.56434</v>
       </c>
       <c r="E3" t="n">
-        <v>17.02722</v>
+        <v>16.78797</v>
       </c>
       <c r="F3" t="n">
-        <v>42.43711</v>
+        <v>42.5976</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05016</v>
+        <v>0.05103</v>
       </c>
       <c r="H3" t="n">
-        <v>1.76122</v>
+        <v>1.80809</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13272</v>
+        <v>16.79216</v>
       </c>
       <c r="D4" t="n">
-        <v>16.47164</v>
+        <v>16.4046</v>
       </c>
       <c r="E4" t="n">
-        <v>16.86633</v>
+        <v>16.44514</v>
       </c>
       <c r="F4" t="n">
-        <v>43.28951</v>
+        <v>41.415</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0505</v>
+        <v>0.05064</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83009</v>
+        <v>1.80565</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64052</v>
+        <v>16.61739</v>
       </c>
       <c r="D6" t="n">
-        <v>15.88673</v>
+        <v>16.21401</v>
       </c>
       <c r="E6" t="n">
-        <v>16.23705</v>
+        <v>16.55685</v>
       </c>
       <c r="F6" t="n">
-        <v>21.91582</v>
+        <v>21.80995</v>
       </c>
       <c r="G6" t="n">
-        <v>34.35522</v>
+        <v>34.01274</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54896</v>
+        <v>16.81924</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95236</v>
+        <v>16.12876</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38</v>
+        <v>16.13056</v>
       </c>
       <c r="F7" t="n">
-        <v>21.47348</v>
+        <v>21.71874</v>
       </c>
       <c r="G7" t="n">
-        <v>34.18519</v>
+        <v>34.31468</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.09916</v>
+        <v>16.46907</v>
       </c>
       <c r="D8" t="n">
-        <v>16.22783</v>
+        <v>15.93106</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51601</v>
+        <v>16.1037</v>
       </c>
       <c r="F8" t="n">
-        <v>21.53015</v>
+        <v>21.76486</v>
       </c>
       <c r="G8" t="n">
-        <v>33.97571</v>
+        <v>33.98675</v>
       </c>
     </row>
   </sheetData>
